--- a/artfynd/A 23460-2025 artfynd.xlsx
+++ b/artfynd/A 23460-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118036260</v>
+        <v>87638397</v>
       </c>
       <c r="B2" t="n">
-        <v>102758</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222002</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Harrån_slammeråsen, Jmt</t>
+          <t>Storharrsjövägen intill E14, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531584</v>
+        <v>531610</v>
       </c>
       <c r="R2" t="n">
-        <v>6947941</v>
+        <v>6947932</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2020-08-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,21 +762,226 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Skogsväg</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Kerstin Frostberg</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Kerstin Frostberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>54854977</v>
+      </c>
+      <c r="B3" t="n">
+        <v>102464</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Slammeråsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>531612</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6947864</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2015-08-15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2015-08-15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell, Jan Edelsjö</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118036260</v>
+      </c>
+      <c r="B4" t="n">
+        <v>103683</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Harrån_slammeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>531584</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6947941</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Håkan Blomqvist</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Håkan Blomqvist</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23460-2025 artfynd.xlsx
+++ b/artfynd/A 23460-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87638397</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54854977</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,8 +997,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118036260</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>